--- a/order_forms/034_promo_order_form--order_forms.xlsx
+++ b/order_forms/034_promo_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1194,17 +1194,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>price_currency_choices</t>
+          <t>order_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cny</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>order_type_choices</t>
+          <t>promo_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>promo_status_choices</t>
+          <t>order_currency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>jpy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jpy</t>
+          <t>cny</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>CNY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>order_currency_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cny</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>order_currency_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cny</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1369,78 +1369,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_source_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_source_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>order_source_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>order_source_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
